--- a/src/main/resources/doc/PONKIDS-테이블정의서_v4.6.xlsx
+++ b/src/main/resources/doc/PONKIDS-테이블정의서_v4.6.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jjeoV/Desktop/jjeoV/2023/pioneerKids/workspace/ponkidsDev/ponkids/src/main/resources/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76F15B3D-9415-2149-8266-BD34CCC6939D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F76185CC-CDFF-5347-89AC-7AED48ACE682}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20" yWindow="1180" windowWidth="38400" windowHeight="21100" tabRatio="777" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" tabRatio="777" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="테이블정의서" sheetId="26" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5025" uniqueCount="885">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5024" uniqueCount="885">
   <si>
     <t>테이블명</t>
     <phoneticPr fontId="12" type="noConversion"/>
@@ -20389,9 +20389,7 @@
       <c r="I168" s="101" t="s">
         <v>233</v>
       </c>
-      <c r="J168" s="45" t="s">
-        <v>191</v>
-      </c>
+      <c r="J168" s="45"/>
       <c r="K168" s="45"/>
       <c r="L168" s="45"/>
       <c r="M168" s="45"/>
@@ -20419,7 +20417,7 @@
       </c>
       <c r="AA168" s="125" t="str">
         <f t="shared" si="51"/>
-        <v>REVIEW_GRADE VARCHAR(10) NOT NULL,</v>
+        <v>REVIEW_GRADE VARCHAR(10),</v>
       </c>
       <c r="AB168" s="125" t="str">
         <f t="shared" si="49"/>
@@ -20447,7 +20445,7 @@
       </c>
       <c r="AH168" s="131" t="str">
         <f t="shared" si="45"/>
-        <v>ALTER TABLE TB_CLASS_REVIEW ADD COLUMN REVIEW_GRADE VARCHAR(10) NOT NULL;</v>
+        <v>ALTER TABLE TB_CLASS_REVIEW ADD COLUMN REVIEW_GRADE VARCHAR(10);</v>
       </c>
       <c r="AI168" s="125" t="str">
         <f t="shared" si="54"/>
